--- a/screens/Clinic_Management_SaaS_Laravel13_React_Full_Product_Package_Register.xlsx
+++ b/screens/Clinic_Management_SaaS_Laravel13_React_Full_Product_Package_Register.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Laravel Projects\clinic-management-system-new\screens\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCDA469-2755-4460-8AC7-3FB54302A05A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="11918" yWindow="0" windowWidth="12165" windowHeight="14362" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="1" r:id="rId1"/>
@@ -21,12 +27,12 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Frontend Packages'!$A$1:$J$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Recommended Install Plan'!$A$1:$I$25</definedName>
   </definedNames>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1095" uniqueCount="787">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="787">
   <si>
     <t>CLINIC MANAGEMENT SAAS — FULL PRODUCT PACKAGE REGISTER</t>
   </si>
@@ -2392,8 +2398,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2418,7 +2424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2455,6 +2461,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -2483,11 +2501,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -2503,19 +2518,38 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2553,7 +2587,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2587,6 +2621,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2621,9 +2656,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2796,109 +2832,109 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="100.7109375" customWidth="1"/>
-    <col min="4" max="4" width="28.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.73046875" customWidth="1"/>
+    <col min="2" max="2" width="100.73046875" customWidth="1"/>
+    <col min="4" max="4" width="28.73046875" customWidth="1"/>
+    <col min="5" max="5" width="16.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="19.5" x14ac:dyDescent="0.6">
+      <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="1" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="2">
         <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E6" s="2">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="3">
+      <c r="E7" s="2">
         <v>78</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:6" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>14</v>
       </c>
     </row>
@@ -2911,3494 +2947,3494 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" customWidth="1"/>
-    <col min="3" max="3" width="32.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="60.7109375" customWidth="1"/>
-    <col min="6" max="6" width="62.7109375" customWidth="1"/>
-    <col min="7" max="7" width="48.7109375" customWidth="1"/>
-    <col min="8" max="8" width="34.7109375" customWidth="1"/>
-    <col min="9" max="9" width="30.7109375" customWidth="1"/>
-    <col min="10" max="10" width="62.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="2" max="2" width="20.73046875" customWidth="1"/>
+    <col min="3" max="3" width="32.73046875" customWidth="1"/>
+    <col min="4" max="4" width="22.73046875" customWidth="1"/>
+    <col min="5" max="5" width="60.73046875" customWidth="1"/>
+    <col min="6" max="6" width="62.73046875" customWidth="1"/>
+    <col min="7" max="7" width="48.73046875" customWidth="1"/>
+    <col min="8" max="8" width="34.73046875" customWidth="1"/>
+    <col min="9" max="9" width="30.73046875" customWidth="1"/>
+    <col min="10" max="10" width="62.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
         <v>38</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="7" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="I4" s="5" t="s">
+      <c r="I4" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="7" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="7" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="7" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="7" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="7" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="5" t="s">
+    <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>84</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="7" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="5" t="s">
+    <row r="9" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A9" s="9" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="9" t="s">
         <v>94</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="9" t="s">
         <v>95</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="9" t="s">
         <v>96</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="5" t="s">
+      <c r="J9" s="9" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="6" t="s">
+    <row r="10" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A10" s="9" t="s">
         <v>100</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="9" t="s">
         <v>102</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="9" t="s">
         <v>103</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="9" t="s">
         <v>105</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="9" t="s">
         <v>107</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="9" t="s">
         <v>108</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="9" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="6" t="s">
+    <row r="11" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="7" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="7" t="s">
         <v>126</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="E13" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="7" t="s">
         <v>131</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="G13" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J13" s="5" t="s">
+      <c r="J13" s="7" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="4" t="s">
+    <row r="14" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
         <v>135</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="7" t="s">
         <v>139</v>
       </c>
-      <c r="F14" s="4" t="s">
+      <c r="F14" s="7" t="s">
         <v>140</v>
       </c>
-      <c r="G14" s="4" t="s">
+      <c r="G14" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="H14" s="4" t="s">
+      <c r="H14" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="I14" s="4" t="s">
+      <c r="I14" s="7" t="s">
         <v>143</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="7" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="4" t="s">
+    <row r="15" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
         <v>145</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>146</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="7" t="s">
         <v>147</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J15" s="4" t="s">
+      <c r="J15" s="7" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="6" t="s">
+    <row r="16" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="7" t="s">
         <v>157</v>
       </c>
-      <c r="F16" s="6" t="s">
+      <c r="F16" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="7" t="s">
         <v>159</v>
       </c>
-      <c r="H16" s="6" t="s">
+      <c r="H16" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I16" s="6" t="s">
+      <c r="I16" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J16" s="6" t="s">
+      <c r="J16" s="7" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="6" t="s">
+    <row r="17" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>163</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="C17" s="6" t="s">
+      <c r="C17" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="F17" s="6" t="s">
+      <c r="F17" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H17" s="6" t="s">
+      <c r="H17" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="I17" s="6" t="s">
+      <c r="I17" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="J17" s="6" t="s">
+      <c r="J17" s="7" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>171</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="7" t="s">
         <v>176</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="7" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="6" t="s">
+    <row r="19" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>178</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="C19" s="6" t="s">
+      <c r="C19" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E19" s="6" t="s">
+      <c r="E19" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="F19" s="6" t="s">
+      <c r="F19" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="G19" s="6" t="s">
+      <c r="G19" s="7" t="s">
         <v>183</v>
       </c>
-      <c r="H19" s="6" t="s">
+      <c r="H19" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I19" s="6" t="s">
+      <c r="I19" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J19" s="6" t="s">
+      <c r="J19" s="7" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="7" t="s">
         <v>185</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>186</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="7" t="s">
         <v>190</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J20" s="7" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="4" t="s">
+    <row r="21" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="7" t="s">
         <v>196</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="7" t="s">
         <v>197</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="7" t="s">
         <v>198</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="7" t="s">
         <v>199</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="7" t="s">
         <v>201</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="5" t="s">
+    <row r="22" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
         <v>202</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E22" s="5" t="s">
+      <c r="E22" s="7" t="s">
         <v>205</v>
       </c>
-      <c r="F22" s="5" t="s">
+      <c r="F22" s="7" t="s">
         <v>206</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="H22" s="5" t="s">
+      <c r="H22" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="I22" s="5" t="s">
+      <c r="I22" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="7" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="6" t="s">
+    <row r="23" spans="1:10" s="10" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A23" s="9" t="s">
         <v>209</v>
       </c>
-      <c r="B23" s="6" t="s">
+      <c r="B23" s="9" t="s">
         <v>210</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="C23" s="9" t="s">
         <v>211</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D23" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="E23" s="9" t="s">
         <v>212</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="F23" s="9" t="s">
         <v>213</v>
       </c>
-      <c r="G23" s="6" t="s">
+      <c r="G23" s="9" t="s">
         <v>214</v>
       </c>
-      <c r="H23" s="6" t="s">
+      <c r="H23" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="I23" s="6" t="s">
+      <c r="I23" s="9" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="6" t="s">
+    <row r="24" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C24" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="D24" s="6" t="s">
+      <c r="D24" s="7" t="s">
         <v>219</v>
       </c>
-      <c r="E24" s="6" t="s">
+      <c r="E24" s="7" t="s">
         <v>220</v>
       </c>
-      <c r="F24" s="6" t="s">
+      <c r="F24" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G24" s="6" t="s">
+      <c r="G24" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H24" s="6" t="s">
+      <c r="H24" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J24" s="6" t="s">
+      <c r="J24" s="7" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>226</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>227</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="7" t="s">
         <v>230</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="7" t="s">
         <v>160</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="7" t="s">
         <v>231</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="5" t="s">
+    <row r="26" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="7" t="s">
         <v>233</v>
       </c>
-      <c r="B26" s="5" t="s">
+      <c r="B26" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="7" t="s">
         <v>235</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E26" s="5" t="s">
+      <c r="E26" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="F26" s="5" t="s">
+      <c r="F26" s="7" t="s">
         <v>237</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="7" t="s">
         <v>238</v>
       </c>
-      <c r="H26" s="5" t="s">
+      <c r="H26" s="7" t="s">
         <v>239</v>
       </c>
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="7" t="s">
         <v>240</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="5" t="s">
+    <row r="27" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A27" s="7" t="s">
         <v>242</v>
       </c>
-      <c r="B27" s="5" t="s">
+      <c r="B27" s="7" t="s">
         <v>243</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="7" t="s">
         <v>244</v>
       </c>
-      <c r="D27" s="5" t="s">
+      <c r="D27" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="5" t="s">
+      <c r="E27" s="7" t="s">
         <v>245</v>
       </c>
-      <c r="F27" s="5" t="s">
+      <c r="F27" s="7" t="s">
         <v>246</v>
       </c>
-      <c r="G27" s="5" t="s">
+      <c r="G27" s="7" t="s">
         <v>247</v>
       </c>
-      <c r="H27" s="5" t="s">
+      <c r="H27" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J27" s="5" t="s">
+      <c r="J27" s="7" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="5" t="s">
+    <row r="28" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="B28" s="5" t="s">
+      <c r="B28" s="7" t="s">
         <v>252</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="7" t="s">
         <v>253</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="5" t="s">
+      <c r="E28" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="F28" s="5" t="s">
+      <c r="F28" s="7" t="s">
         <v>255</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="7" t="s">
         <v>256</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="H28" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="7" t="s">
         <v>257</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="7" t="s">
         <v>258</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="5" t="s">
+    <row r="29" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="7" t="s">
         <v>259</v>
       </c>
-      <c r="B29" s="5" t="s">
+      <c r="B29" s="7" t="s">
         <v>260</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="D29" s="5" t="s">
+      <c r="D29" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E29" s="5" t="s">
+      <c r="E29" s="7" t="s">
         <v>262</v>
       </c>
-      <c r="F29" s="5" t="s">
+      <c r="F29" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="G29" s="5" t="s">
+      <c r="G29" s="7" t="s">
         <v>264</v>
       </c>
-      <c r="H29" s="5" t="s">
+      <c r="H29" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I29" s="5" t="s">
+      <c r="I29" s="7" t="s">
         <v>265</v>
       </c>
-      <c r="J29" s="5" t="s">
+      <c r="J29" s="7" t="s">
         <v>266</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="6" t="s">
+    <row r="30" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="7" t="s">
         <v>267</v>
       </c>
-      <c r="B30" s="6" t="s">
+      <c r="B30" s="7" t="s">
         <v>268</v>
       </c>
-      <c r="C30" s="6" t="s">
+      <c r="C30" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="D30" s="6" t="s">
+      <c r="D30" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E30" s="6" t="s">
+      <c r="E30" s="7" t="s">
         <v>270</v>
       </c>
-      <c r="F30" s="6" t="s">
+      <c r="F30" s="7" t="s">
         <v>271</v>
       </c>
-      <c r="G30" s="6" t="s">
+      <c r="G30" s="7" t="s">
         <v>272</v>
       </c>
-      <c r="H30" s="6" t="s">
+      <c r="H30" s="7" t="s">
         <v>273</v>
       </c>
-      <c r="I30" s="6" t="s">
+      <c r="I30" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="J30" s="6" t="s">
+      <c r="J30" s="7" t="s">
         <v>274</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="6" t="s">
+    <row r="31" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A31" s="7" t="s">
         <v>275</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>277</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D31" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E31" s="7" t="s">
         <v>278</v>
       </c>
-      <c r="F31" s="6" t="s">
+      <c r="F31" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="G31" s="6" t="s">
+      <c r="G31" s="7" t="s">
         <v>280</v>
       </c>
-      <c r="H31" s="6" t="s">
+      <c r="H31" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="I31" s="6" t="s">
+      <c r="I31" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="J31" s="6" t="s">
+      <c r="J31" s="7" t="s">
         <v>282</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J31" xr:uid="{00000000-0009-0000-0000-000001000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:J39"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="23.7109375" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="66.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
-    <col min="7" max="7" width="42.7109375" customWidth="1"/>
-    <col min="8" max="9" width="26.7109375" customWidth="1"/>
-    <col min="10" max="10" width="70.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="2" max="2" width="23.73046875" customWidth="1"/>
+    <col min="3" max="3" width="34.73046875" customWidth="1"/>
+    <col min="4" max="4" width="22.73046875" customWidth="1"/>
+    <col min="5" max="5" width="66.73046875" customWidth="1"/>
+    <col min="6" max="6" width="60.73046875" customWidth="1"/>
+    <col min="7" max="7" width="42.73046875" customWidth="1"/>
+    <col min="8" max="9" width="26.73046875" customWidth="1"/>
+    <col min="10" max="10" width="70.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A2" s="7" t="s">
         <v>285</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>287</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>288</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="7" t="s">
         <v>289</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="7" t="s">
         <v>292</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="7" t="s">
         <v>293</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A3" s="7" t="s">
         <v>294</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>295</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
         <v>296</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="7" t="s">
         <v>297</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="7" t="s">
         <v>298</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="7" t="s">
         <v>299</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="7" t="s">
         <v>300</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="7" t="s">
         <v>301</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>303</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>305</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="7" t="s">
         <v>307</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="7" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="7" t="s">
         <v>313</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="7" t="s">
         <v>319</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A6" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="7" t="s">
         <v>322</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>323</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="7" t="s">
         <v>324</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="7" t="s">
         <v>325</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="7" t="s">
         <v>326</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="7" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="6" t="s">
+    <row r="7" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A7" s="7" t="s">
         <v>328</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>329</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="7" t="s">
         <v>330</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="7" t="s">
         <v>331</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="7" t="s">
         <v>332</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="7" t="s">
         <v>333</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="7" t="s">
         <v>334</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="7" t="s">
         <v>335</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A8" s="7" t="s">
         <v>336</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="7" t="s">
         <v>338</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="7" t="s">
         <v>339</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="7" t="s">
         <v>340</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="7" t="s">
         <v>341</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="7" t="s">
         <v>342</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="7" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A9" s="7" t="s">
         <v>344</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>345</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="7" t="s">
         <v>346</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="7" t="s">
         <v>347</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="7" t="s">
         <v>348</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="7" t="s">
         <v>349</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="7" t="s">
         <v>350</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="7" t="s">
         <v>351</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A10" s="7" t="s">
         <v>352</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>353</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="7" t="s">
         <v>354</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="7" t="s">
         <v>355</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="7" t="s">
         <v>356</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="7" t="s">
         <v>357</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="7" t="s">
         <v>358</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="7" t="s">
         <v>359</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A11" s="7" t="s">
         <v>360</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="7" t="s">
         <v>361</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="7" t="s">
         <v>362</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="7" t="s">
         <v>363</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="7" t="s">
         <v>364</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="7" t="s">
         <v>365</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="7" t="s">
         <v>366</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="7" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="4" t="s">
+    <row r="12" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="7" t="s">
         <v>368</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="7" t="s">
         <v>369</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="7" t="s">
         <v>370</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="7" t="s">
         <v>371</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="F12" s="7" t="s">
         <v>372</v>
       </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="7" t="s">
         <v>373</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="7" t="s">
         <v>374</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="4" t="s">
+    <row r="13" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="7" t="s">
         <v>375</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>376</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="7" t="s">
         <v>378</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="F13" s="7" t="s">
         <v>379</v>
       </c>
-      <c r="G13" s="4" t="s">
+      <c r="G13" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="7" t="s">
         <v>377</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="7" t="s">
         <v>381</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A14" s="7" t="s">
         <v>382</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="7" t="s">
         <v>383</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="7" t="s">
         <v>384</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="7" t="s">
         <v>385</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="7" t="s">
         <v>386</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="7" t="s">
         <v>387</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="7" t="s">
         <v>388</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="7" t="s">
         <v>389</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A15" s="7" t="s">
         <v>390</v>
       </c>
-      <c r="B15" s="5" t="s">
+      <c r="B15" s="7" t="s">
         <v>391</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="7" t="s">
         <v>392</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E15" s="5" t="s">
+      <c r="E15" s="7" t="s">
         <v>393</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="7" t="s">
         <v>394</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="G15" s="7" t="s">
         <v>395</v>
       </c>
-      <c r="H15" s="5" t="s">
+      <c r="H15" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I15" s="5" t="s">
+      <c r="I15" s="7" t="s">
         <v>396</v>
       </c>
-      <c r="J15" s="5" t="s">
+      <c r="J15" s="7" t="s">
         <v>397</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="7" t="s">
         <v>398</v>
       </c>
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="7" t="s">
         <v>399</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="7" t="s">
         <v>400</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="5" t="s">
+      <c r="E16" s="7" t="s">
         <v>401</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="7" t="s">
         <v>402</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="7" t="s">
         <v>403</v>
       </c>
-      <c r="H16" s="5" t="s">
+      <c r="H16" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I16" s="5" t="s">
+      <c r="I16" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="7" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A17" s="7" t="s">
         <v>406</v>
       </c>
-      <c r="B17" s="5" t="s">
+      <c r="B17" s="7" t="s">
         <v>407</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="7" t="s">
         <v>408</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E17" s="5" t="s">
+      <c r="E17" s="7" t="s">
         <v>409</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="7" t="s">
         <v>410</v>
       </c>
-      <c r="G17" s="5" t="s">
+      <c r="G17" s="7" t="s">
         <v>411</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I17" s="5" t="s">
+      <c r="I17" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="J17" s="5" t="s">
+      <c r="J17" s="7" t="s">
         <v>413</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="B18" s="5" t="s">
+      <c r="B18" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="7" t="s">
         <v>416</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E18" s="5" t="s">
+      <c r="E18" s="7" t="s">
         <v>417</v>
       </c>
-      <c r="F18" s="5" t="s">
+      <c r="F18" s="7" t="s">
         <v>418</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I18" s="5" t="s">
+      <c r="I18" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="7" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="5" t="s">
+    <row r="19" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="7" t="s">
         <v>422</v>
       </c>
-      <c r="B19" s="5" t="s">
+      <c r="B19" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="7" t="s">
         <v>423</v>
       </c>
-      <c r="D19" s="5" t="s">
+      <c r="D19" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="5" t="s">
+      <c r="E19" s="7" t="s">
         <v>424</v>
       </c>
-      <c r="F19" s="5" t="s">
+      <c r="F19" s="7" t="s">
         <v>425</v>
       </c>
-      <c r="G19" s="5" t="s">
+      <c r="G19" s="7" t="s">
         <v>426</v>
       </c>
-      <c r="H19" s="5" t="s">
+      <c r="H19" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I19" s="5" t="s">
+      <c r="I19" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="J19" s="5" t="s">
+      <c r="J19" s="7" t="s">
         <v>427</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="5" t="s">
+    <row r="20" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A20" s="7" t="s">
         <v>428</v>
       </c>
-      <c r="B20" s="5" t="s">
+      <c r="B20" s="7" t="s">
         <v>415</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>429</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E20" s="5" t="s">
+      <c r="E20" s="7" t="s">
         <v>430</v>
       </c>
-      <c r="F20" s="5" t="s">
+      <c r="F20" s="7" t="s">
         <v>431</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="7" t="s">
         <v>432</v>
       </c>
-      <c r="H20" s="5" t="s">
+      <c r="H20" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I20" s="5" t="s">
+      <c r="I20" s="7" t="s">
         <v>420</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="7" t="s">
         <v>433</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="5" t="s">
+    <row r="21" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A21" s="7" t="s">
         <v>434</v>
       </c>
-      <c r="B21" s="5" t="s">
+      <c r="B21" s="7" t="s">
         <v>435</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="7" t="s">
         <v>436</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E21" s="5" t="s">
+      <c r="E21" s="7" t="s">
         <v>437</v>
       </c>
-      <c r="F21" s="5" t="s">
+      <c r="F21" s="7" t="s">
         <v>438</v>
       </c>
-      <c r="G21" s="5" t="s">
+      <c r="G21" s="7" t="s">
         <v>419</v>
       </c>
-      <c r="H21" s="5" t="s">
+      <c r="H21" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I21" s="5" t="s">
+      <c r="I21" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J21" s="5" t="s">
+      <c r="J21" s="7" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="6" t="s">
+    <row r="22" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="7" t="s">
         <v>440</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B22" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C22" s="7" t="s">
         <v>442</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D22" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E22" s="6" t="s">
+      <c r="E22" s="7" t="s">
         <v>443</v>
       </c>
-      <c r="F22" s="6" t="s">
+      <c r="F22" s="7" t="s">
         <v>444</v>
       </c>
-      <c r="G22" s="6" t="s">
+      <c r="G22" s="7" t="s">
         <v>445</v>
       </c>
-      <c r="H22" s="6" t="s">
+      <c r="H22" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I22" s="6" t="s">
+      <c r="I22" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J22" s="6" t="s">
+      <c r="J22" s="7" t="s">
         <v>446</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="5" t="s">
+    <row r="23" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A23" s="7" t="s">
         <v>447</v>
       </c>
-      <c r="B23" s="5" t="s">
+      <c r="B23" s="7" t="s">
         <v>448</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="D23" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E23" s="5" t="s">
+      <c r="E23" s="7" t="s">
         <v>450</v>
       </c>
-      <c r="F23" s="5" t="s">
+      <c r="F23" s="7" t="s">
         <v>451</v>
       </c>
-      <c r="G23" s="5" t="s">
+      <c r="G23" s="7" t="s">
         <v>452</v>
       </c>
-      <c r="H23" s="5" t="s">
+      <c r="H23" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I23" s="5" t="s">
+      <c r="I23" s="7" t="s">
         <v>449</v>
       </c>
-      <c r="J23" s="5" t="s">
+      <c r="J23" s="7" t="s">
         <v>453</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="5" t="s">
+    <row r="24" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A24" s="7" t="s">
         <v>454</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="7" t="s">
         <v>455</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="7" t="s">
         <v>456</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E24" s="5" t="s">
+      <c r="E24" s="7" t="s">
         <v>457</v>
       </c>
-      <c r="F24" s="5" t="s">
+      <c r="F24" s="7" t="s">
         <v>458</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="7" t="s">
         <v>459</v>
       </c>
-      <c r="H24" s="5" t="s">
+      <c r="H24" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I24" s="5" t="s">
+      <c r="I24" s="7" t="s">
         <v>460</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="7" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="6" t="s">
+    <row r="25" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="7" t="s">
         <v>462</v>
       </c>
-      <c r="B25" s="6" t="s">
+      <c r="B25" s="7" t="s">
         <v>463</v>
       </c>
-      <c r="C25" s="6" t="s">
+      <c r="C25" s="7" t="s">
         <v>464</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D25" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E25" s="6" t="s">
+      <c r="E25" s="7" t="s">
         <v>465</v>
       </c>
-      <c r="F25" s="6" t="s">
+      <c r="F25" s="7" t="s">
         <v>466</v>
       </c>
-      <c r="G25" s="6" t="s">
+      <c r="G25" s="7" t="s">
         <v>467</v>
       </c>
-      <c r="H25" s="6" t="s">
+      <c r="H25" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I25" s="6" t="s">
+      <c r="I25" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J25" s="6" t="s">
+      <c r="J25" s="7" t="s">
         <v>468</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="6" t="s">
+    <row r="26" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="7" t="s">
         <v>469</v>
       </c>
-      <c r="B26" s="6" t="s">
+      <c r="B26" s="7" t="s">
         <v>470</v>
       </c>
-      <c r="C26" s="6" t="s">
+      <c r="C26" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="D26" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E26" s="6" t="s">
+      <c r="E26" s="7" t="s">
         <v>472</v>
       </c>
-      <c r="F26" s="6" t="s">
+      <c r="F26" s="7" t="s">
         <v>473</v>
       </c>
-      <c r="G26" s="6" t="s">
+      <c r="G26" s="7" t="s">
         <v>474</v>
       </c>
-      <c r="H26" s="6" t="s">
+      <c r="H26" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I26" s="6" t="s">
+      <c r="I26" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J26" s="6" t="s">
+      <c r="J26" s="7" t="s">
         <v>475</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="6" t="s">
+    <row r="27" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A27" s="7" t="s">
         <v>476</v>
       </c>
-      <c r="B27" s="6" t="s">
+      <c r="B27" s="7" t="s">
         <v>477</v>
       </c>
-      <c r="C27" s="6" t="s">
+      <c r="C27" s="7" t="s">
         <v>478</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="D27" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E27" s="6" t="s">
+      <c r="E27" s="7" t="s">
         <v>479</v>
       </c>
-      <c r="F27" s="6" t="s">
+      <c r="F27" s="7" t="s">
         <v>480</v>
       </c>
-      <c r="G27" s="6" t="s">
+      <c r="G27" s="7" t="s">
         <v>481</v>
       </c>
-      <c r="H27" s="6" t="s">
+      <c r="H27" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I27" s="6" t="s">
+      <c r="I27" s="7" t="s">
         <v>482</v>
       </c>
-      <c r="J27" s="6" t="s">
+      <c r="J27" s="7" t="s">
         <v>483</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="4" t="s">
+    <row r="28" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A28" s="7" t="s">
         <v>484</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="7" t="s">
         <v>485</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="7" t="s">
         <v>486</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="7" t="s">
         <v>487</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="7" t="s">
         <v>488</v>
       </c>
-      <c r="F28" s="4" t="s">
+      <c r="F28" s="7" t="s">
         <v>489</v>
       </c>
-      <c r="G28" s="4" t="s">
+      <c r="G28" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H28" s="4" t="s">
+      <c r="H28" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I28" s="4" t="s">
+      <c r="I28" s="7" t="s">
         <v>490</v>
       </c>
-      <c r="J28" s="4" t="s">
+      <c r="J28" s="7" t="s">
         <v>491</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="4" t="s">
+    <row r="29" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A29" s="7" t="s">
         <v>492</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="7" t="s">
         <v>493</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="7" t="s">
         <v>494</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="7" t="s">
         <v>496</v>
       </c>
-      <c r="F29" s="4" t="s">
+      <c r="F29" s="7" t="s">
         <v>497</v>
       </c>
-      <c r="G29" s="4" t="s">
+      <c r="G29" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H29" s="4" t="s">
+      <c r="H29" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="I29" s="4" t="s">
+      <c r="I29" s="7" t="s">
         <v>499</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="4" t="s">
+    <row r="30" spans="1:10" s="8" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A30" s="7" t="s">
         <v>500</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="7" t="s">
         <v>501</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="7" t="s">
         <v>502</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="7" t="s">
         <v>495</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="7" t="s">
         <v>503</v>
       </c>
-      <c r="F30" s="4" t="s">
+      <c r="F30" s="7" t="s">
         <v>504</v>
       </c>
-      <c r="G30" s="4" t="s">
+      <c r="G30" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H30" s="4" t="s">
+      <c r="H30" s="7" t="s">
         <v>498</v>
       </c>
-      <c r="I30" s="4" t="s">
+      <c r="I30" s="7" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="4" t="s">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A31" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F31" s="4" t="s">
+      <c r="F31" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G31" s="4" t="s">
+      <c r="G31" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="H31" s="4" t="s">
+      <c r="H31" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="I31" s="4" t="s">
+      <c r="I31" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="J31" s="4" t="s">
+      <c r="J31" s="3" t="s">
         <v>514</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="4" t="s">
+    <row r="32" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="7" t="s">
         <v>515</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="7" t="s">
         <v>517</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="7" t="s">
         <v>518</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="F32" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="G32" s="4" t="s">
+      <c r="G32" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H32" s="4" t="s">
+      <c r="H32" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I32" s="4" t="s">
+      <c r="I32" s="7" t="s">
         <v>520</v>
       </c>
-      <c r="J32" s="4" t="s">
+      <c r="J32" s="7" t="s">
         <v>521</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
-      <c r="A33" s="4" t="s">
+    <row r="33" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="7" t="s">
         <v>522</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="C33" s="4" t="s">
+      <c r="C33" s="7" t="s">
         <v>524</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="7" t="s">
         <v>525</v>
       </c>
-      <c r="F33" s="4" t="s">
+      <c r="F33" s="7" t="s">
         <v>526</v>
       </c>
-      <c r="G33" s="4" t="s">
+      <c r="G33" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H33" s="4" t="s">
+      <c r="H33" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I33" s="4" t="s">
+      <c r="I33" s="7" t="s">
         <v>527</v>
       </c>
-      <c r="J33" s="4" t="s">
+      <c r="J33" s="7" t="s">
         <v>528</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
-      <c r="A34" s="5" t="s">
+    <row r="34" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A34" s="7" t="s">
         <v>529</v>
       </c>
-      <c r="B34" s="5" t="s">
+      <c r="B34" s="7" t="s">
         <v>530</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="7" t="s">
         <v>531</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="5" t="s">
+      <c r="E34" s="7" t="s">
         <v>532</v>
       </c>
-      <c r="F34" s="5" t="s">
+      <c r="F34" s="7" t="s">
         <v>533</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="7" t="s">
         <v>534</v>
       </c>
-      <c r="H34" s="5" t="s">
+      <c r="H34" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I34" s="5" t="s">
+      <c r="I34" s="7" t="s">
         <v>309</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="7" t="s">
         <v>535</v>
       </c>
     </row>
-    <row r="35" spans="1:10">
-      <c r="A35" s="4" t="s">
+    <row r="35" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A35" s="7" t="s">
         <v>536</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="7" t="s">
         <v>537</v>
       </c>
-      <c r="C35" s="4" t="s">
+      <c r="C35" s="7" t="s">
         <v>538</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="7" t="s">
         <v>539</v>
       </c>
-      <c r="F35" s="4" t="s">
+      <c r="F35" s="7" t="s">
         <v>540</v>
       </c>
-      <c r="G35" s="4" t="s">
+      <c r="G35" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H35" s="4" t="s">
+      <c r="H35" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I35" s="4" t="s">
+      <c r="I35" s="7" t="s">
         <v>541</v>
       </c>
-      <c r="J35" s="4" t="s">
+      <c r="J35" s="7" t="s">
         <v>542</v>
       </c>
     </row>
-    <row r="36" spans="1:10">
-      <c r="A36" s="5" t="s">
+    <row r="36" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="7" t="s">
         <v>543</v>
       </c>
-      <c r="B36" s="5" t="s">
+      <c r="B36" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="7" t="s">
         <v>545</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E36" s="5" t="s">
+      <c r="E36" s="7" t="s">
         <v>546</v>
       </c>
-      <c r="F36" s="5" t="s">
+      <c r="F36" s="7" t="s">
         <v>547</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="H36" s="5" t="s">
+      <c r="H36" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I36" s="5" t="s">
+      <c r="I36" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="7" t="s">
         <v>549</v>
       </c>
     </row>
-    <row r="37" spans="1:10">
-      <c r="A37" s="5" t="s">
+    <row r="37" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="7" t="s">
         <v>550</v>
       </c>
-      <c r="B37" s="5" t="s">
+      <c r="B37" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="7" t="s">
         <v>552</v>
       </c>
-      <c r="D37" s="5" t="s">
+      <c r="D37" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E37" s="5" t="s">
+      <c r="E37" s="7" t="s">
         <v>553</v>
       </c>
-      <c r="F37" s="5" t="s">
+      <c r="F37" s="7" t="s">
         <v>554</v>
       </c>
-      <c r="G37" s="5" t="s">
+      <c r="G37" s="7" t="s">
         <v>290</v>
       </c>
-      <c r="H37" s="5" t="s">
+      <c r="H37" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I37" s="5" t="s">
+      <c r="I37" s="7" t="s">
         <v>551</v>
       </c>
-      <c r="J37" s="5" t="s">
+      <c r="J37" s="7" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="38" spans="1:10">
-      <c r="A38" s="5" t="s">
+    <row r="38" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A38" s="7" t="s">
         <v>556</v>
       </c>
-      <c r="B38" s="5" t="s">
+      <c r="B38" s="7" t="s">
         <v>557</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="7" t="s">
         <v>558</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="E38" s="5" t="s">
+      <c r="E38" s="7" t="s">
         <v>559</v>
       </c>
-      <c r="F38" s="5" t="s">
+      <c r="F38" s="7" t="s">
         <v>560</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="7" t="s">
         <v>548</v>
       </c>
-      <c r="H38" s="5" t="s">
+      <c r="H38" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I38" s="5" t="s">
+      <c r="I38" s="7" t="s">
         <v>561</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="7" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="39" spans="1:10">
-      <c r="A39" s="6" t="s">
+    <row r="39" spans="1:10" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="s">
         <v>563</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>564</v>
       </c>
-      <c r="C39" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>565</v>
       </c>
-      <c r="D39" s="6" t="s">
+      <c r="D39" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="E39" s="6" t="s">
+      <c r="E39" s="7" t="s">
         <v>566</v>
       </c>
-      <c r="F39" s="6" t="s">
+      <c r="F39" s="7" t="s">
         <v>567</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="7" t="s">
         <v>568</v>
       </c>
-      <c r="H39" s="6" t="s">
+      <c r="H39" s="7" t="s">
         <v>317</v>
       </c>
-      <c r="I39" s="6" t="s">
+      <c r="I39" s="7" t="s">
         <v>249</v>
       </c>
-      <c r="J39" s="6" t="s">
+      <c r="J39" s="7" t="s">
         <v>569</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J39"/>
+  <autoFilter ref="A1:J39" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:J11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="34.7109375" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" customWidth="1"/>
-    <col min="5" max="5" width="65.7109375" customWidth="1"/>
-    <col min="6" max="6" width="60.7109375" customWidth="1"/>
-    <col min="7" max="7" width="40.7109375" customWidth="1"/>
-    <col min="8" max="8" width="28.7109375" customWidth="1"/>
-    <col min="9" max="9" width="24.7109375" customWidth="1"/>
-    <col min="10" max="10" width="65.7109375" customWidth="1"/>
+    <col min="1" max="1" width="12.73046875" customWidth="1"/>
+    <col min="2" max="2" width="24.73046875" customWidth="1"/>
+    <col min="3" max="3" width="34.73046875" customWidth="1"/>
+    <col min="4" max="4" width="22.73046875" customWidth="1"/>
+    <col min="5" max="5" width="65.73046875" customWidth="1"/>
+    <col min="6" max="6" width="60.73046875" customWidth="1"/>
+    <col min="7" max="7" width="40.73046875" customWidth="1"/>
+    <col min="8" max="8" width="28.73046875" customWidth="1"/>
+    <col min="9" max="9" width="24.73046875" customWidth="1"/>
+    <col min="10" max="10" width="65.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>570</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>571</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>572</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>573</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A2" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>580</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A3" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>588</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A4" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>596</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:10" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="G5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="H5" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>604</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A6" s="4" t="s">
         <v>605</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="4" t="s">
         <v>607</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E6" s="5" t="s">
+      <c r="E6" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>611</v>
       </c>
-      <c r="I6" s="5" t="s">
+      <c r="I6" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>613</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="5" t="s">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A7" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>615</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>617</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="4" t="s">
         <v>621</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="4" t="s">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" s="3" t="s">
         <v>622</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>623</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>624</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="3" t="s">
         <v>625</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="3" t="s">
         <v>626</v>
       </c>
-      <c r="G8" s="4" t="s">
+      <c r="G8" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="3" t="s">
         <v>628</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="4" t="s">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A9" s="3" t="s">
         <v>629</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>630</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>631</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="3" t="s">
         <v>632</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="F9" s="3" t="s">
         <v>633</v>
       </c>
-      <c r="G9" s="4" t="s">
+      <c r="G9" s="3" t="s">
         <v>619</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="3" t="s">
         <v>627</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="3" t="s">
         <v>634</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A10" s="3" t="s">
         <v>635</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>636</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>637</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>638</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="F10" s="3" t="s">
         <v>639</v>
       </c>
-      <c r="G10" s="4" t="s">
+      <c r="G10" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="3" t="s">
         <v>640</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="3" t="s">
         <v>641</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="3" t="s">
         <v>642</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A11" s="4" t="s">
         <v>643</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>619</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>647</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="4" t="s">
         <v>648</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J11"/>
+  <autoFilter ref="A1:J11" xr:uid="{00000000-0009-0000-0000-000003000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:I25"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" customWidth="1"/>
-    <col min="2" max="2" width="14.7109375" customWidth="1"/>
-    <col min="3" max="3" width="38.7109375" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" customWidth="1"/>
-    <col min="5" max="5" width="70.7109375" customWidth="1"/>
-    <col min="6" max="6" width="55.7109375" customWidth="1"/>
-    <col min="7" max="7" width="18.7109375" customWidth="1"/>
-    <col min="8" max="8" width="26.7109375" customWidth="1"/>
-    <col min="9" max="9" width="42.7109375" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" customWidth="1"/>
+    <col min="2" max="2" width="14.73046875" customWidth="1"/>
+    <col min="3" max="3" width="38.73046875" customWidth="1"/>
+    <col min="4" max="4" width="25.73046875" customWidth="1"/>
+    <col min="5" max="5" width="70.73046875" customWidth="1"/>
+    <col min="6" max="6" width="55.73046875" customWidth="1"/>
+    <col min="7" max="7" width="18.73046875" customWidth="1"/>
+    <col min="8" max="8" width="26.73046875" customWidth="1"/>
+    <col min="9" max="9" width="42.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>649</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>650</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>651</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>652</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>653</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>654</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>656</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="4">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A2" s="3">
         <v>1</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="3" t="s">
         <v>657</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>658</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="G2" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="H2" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="3" t="s">
         <v>660</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="4">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A3" s="3">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>661</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="G3" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>662</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>663</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="4">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>664</v>
       </c>
-      <c r="G4" s="4" t="s">
+      <c r="G4" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="3" t="s">
         <v>665</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="3" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="5">
+    <row r="5" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>667</v>
       </c>
-      <c r="G5" s="5" t="s">
+      <c r="G5" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>669</v>
       </c>
-      <c r="I5" s="5" t="s">
+      <c r="I5" s="4" t="s">
         <v>670</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="4">
+    <row r="6" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="3" t="s">
         <v>671</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="G6" s="3" t="s">
         <v>672</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="H6" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="3" t="s">
         <v>673</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="5">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E7" s="5" t="s">
+      <c r="E7" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="G7" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="I7" s="5" t="s">
+      <c r="I7" s="4" t="s">
         <v>676</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="5">
+    <row r="8" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E8" s="5" t="s">
+      <c r="E8" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>679</v>
       </c>
-      <c r="I8" s="5" t="s">
+      <c r="I8" s="4" t="s">
         <v>680</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="5">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E9" s="5" t="s">
+      <c r="E9" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="G9" s="5" t="s">
+      <c r="G9" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="I9" s="5" t="s">
+      <c r="I9" s="4" t="s">
         <v>683</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="5">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="5" t="s">
+      <c r="E10" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="4" t="s">
         <v>686</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="5">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E11" s="5" t="s">
+      <c r="E11" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="G11" s="5" t="s">
+      <c r="G11" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>688</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="5">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="E12" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>689</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>685</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="I12" s="5" t="s">
+      <c r="I12" s="4" t="s">
         <v>691</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="6">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A13" s="5">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="5" t="s">
         <v>692</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="5" t="s">
         <v>685</v>
       </c>
-      <c r="H13" s="6" t="s">
+      <c r="H13" s="5" t="s">
         <v>693</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="5" t="s">
         <v>694</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="5">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="B14" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="4" t="s">
         <v>695</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>697</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="I14" s="5" t="s">
+      <c r="I14" s="4" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="4">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A15" s="3">
         <v>14</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="3" t="s">
         <v>700</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="3" t="s">
         <v>702</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>703</v>
       </c>
-      <c r="G15" s="4" t="s">
+      <c r="G15" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="H15" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="I15" s="4" t="s">
+      <c r="I15" s="3" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="4">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A16" s="3">
         <v>15</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>705</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="F16" s="3" t="s">
         <v>706</v>
       </c>
-      <c r="G16" s="4" t="s">
+      <c r="G16" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="H16" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="I16" s="4" t="s">
+      <c r="I16" s="3" t="s">
         <v>708</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="4">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="F17" s="3" t="s">
         <v>709</v>
       </c>
-      <c r="G17" s="4" t="s">
+      <c r="G17" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H17" s="4" t="s">
+      <c r="H17" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="I17" s="4" t="s">
+      <c r="I17" s="3" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="4">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="G18" s="4" t="s">
+      <c r="G18" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I18" s="4" t="s">
+      <c r="I18" s="3" t="s">
         <v>711</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="4">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>712</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>713</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>714</v>
       </c>
-      <c r="G19" s="4" t="s">
+      <c r="G19" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H19" s="4" t="s">
+      <c r="H19" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I19" s="4" t="s">
+      <c r="I19" s="3" t="s">
         <v>715</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="4">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="3" t="s">
         <v>716</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G20" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H20" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I20" s="3" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="4">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>717</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="F21" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="G21" s="4" t="s">
+      <c r="G21" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H21" s="4" t="s">
+      <c r="H21" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I21" s="4" t="s">
+      <c r="I21" s="3" t="s">
         <v>719</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="4">
+    <row r="22" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A22" s="3">
         <v>21</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="3" t="s">
         <v>720</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="3" t="s">
         <v>721</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="3" t="s">
         <v>722</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H22" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I22" s="3" t="s">
         <v>723</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="4">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A23" s="3">
         <v>22</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="3" t="s">
         <v>724</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="3" t="s">
         <v>725</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="F23" s="3" t="s">
         <v>726</v>
       </c>
-      <c r="G23" s="4" t="s">
+      <c r="G23" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H23" s="4" t="s">
+      <c r="H23" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="I23" s="4" t="s">
+      <c r="I23" s="3" t="s">
         <v>727</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="4">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.45">
+      <c r="A24" s="3">
         <v>23</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="3" t="s">
         <v>728</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="3" t="s">
         <v>701</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="3" t="s">
         <v>729</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="F24" s="3" t="s">
         <v>730</v>
       </c>
-      <c r="G24" s="4" t="s">
+      <c r="G24" s="3" t="s">
         <v>659</v>
       </c>
-      <c r="H24" s="4" t="s">
+      <c r="H24" s="3" t="s">
         <v>707</v>
       </c>
-      <c r="I24" s="4" t="s">
+      <c r="I24" s="3" t="s">
         <v>699</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="5">
+    <row r="25" spans="1:9" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="4" t="s">
         <v>731</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="D25" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="E25" s="5" t="s">
+      <c r="E25" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="F25" s="5" t="s">
+      <c r="F25" s="4" t="s">
         <v>733</v>
       </c>
-      <c r="G25" s="5" t="s">
+      <c r="G25" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="H25" s="5" t="s">
+      <c r="H25" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="4" t="s">
         <v>699</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I25"/>
+  <autoFilter ref="A1:I25" xr:uid="{00000000-0009-0000-0000-000004000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="120.7109375" customWidth="1"/>
+    <col min="1" max="1" width="28.73046875" customWidth="1"/>
+    <col min="2" max="2" width="120.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>735</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:2" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>736</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>738</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>741</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>742</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>743</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>747</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>749</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
         <v>485</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
         <v>751</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>752</v>
       </c>
     </row>
@@ -6408,160 +6444,160 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="75.7109375" customWidth="1"/>
-    <col min="3" max="3" width="100.7109375" customWidth="1"/>
+    <col min="1" max="1" width="26.73046875" customWidth="1"/>
+    <col min="2" max="2" width="75.73046875" customWidth="1"/>
+    <col min="3" max="3" width="100.73046875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>753</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>754</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A2" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>757</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A3" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>760</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A4" s="2" t="s">
         <v>761</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>763</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A5" s="2" t="s">
         <v>764</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>766</v>
       </c>
     </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A6" s="2" t="s">
         <v>767</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>768</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>769</v>
       </c>
     </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A7" s="2" t="s">
         <v>770</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>771</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>772</v>
       </c>
     </row>
-    <row r="8" spans="1:3">
-      <c r="A8" s="3" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A8" s="2" t="s">
         <v>773</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>774</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>775</v>
       </c>
     </row>
-    <row r="9" spans="1:3">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A9" s="2" t="s">
         <v>776</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>777</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>778</v>
       </c>
     </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A10" s="2" t="s">
         <v>779</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>780</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A11" s="2" t="s">
         <v>782</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>783</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="12" spans="1:3">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+      <c r="A12" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>785</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>786</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1"/>
-    <hyperlink ref="B3" r:id="rId2"/>
-    <hyperlink ref="B4" r:id="rId3"/>
-    <hyperlink ref="B5" r:id="rId4"/>
-    <hyperlink ref="B6" r:id="rId5"/>
-    <hyperlink ref="B7" r:id="rId6"/>
-    <hyperlink ref="B8" r:id="rId7"/>
-    <hyperlink ref="B9" r:id="rId8"/>
-    <hyperlink ref="B10" r:id="rId9"/>
-    <hyperlink ref="B11" r:id="rId10"/>
-    <hyperlink ref="B12" r:id="rId11"/>
+    <hyperlink ref="B2" r:id="rId1" xr:uid="{00000000-0004-0000-0600-000000000000}"/>
+    <hyperlink ref="B3" r:id="rId2" xr:uid="{00000000-0004-0000-0600-000001000000}"/>
+    <hyperlink ref="B4" r:id="rId3" xr:uid="{00000000-0004-0000-0600-000002000000}"/>
+    <hyperlink ref="B5" r:id="rId4" xr:uid="{00000000-0004-0000-0600-000003000000}"/>
+    <hyperlink ref="B6" r:id="rId5" xr:uid="{00000000-0004-0000-0600-000004000000}"/>
+    <hyperlink ref="B7" r:id="rId6" xr:uid="{00000000-0004-0000-0600-000005000000}"/>
+    <hyperlink ref="B8" r:id="rId7" xr:uid="{00000000-0004-0000-0600-000006000000}"/>
+    <hyperlink ref="B9" r:id="rId8" xr:uid="{00000000-0004-0000-0600-000007000000}"/>
+    <hyperlink ref="B10" r:id="rId9" xr:uid="{00000000-0004-0000-0600-000008000000}"/>
+    <hyperlink ref="B11" r:id="rId10" xr:uid="{00000000-0004-0000-0600-000009000000}"/>
+    <hyperlink ref="B12" r:id="rId11" xr:uid="{00000000-0004-0000-0600-00000A000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
